--- a/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt1_rubricas.xlsx
@@ -1968,13 +1968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C19345B1-06D8-4970-84AA-FF0963BC5918}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19CD4579-3DA7-4907-B5EF-9EFE3BF0FA51}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B6F3E8-95FD-4C81-85B7-E4272214A8B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E09DE1D-CB9F-4B56-ADC3-05D80E4E77BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE26E652-0399-409D-A7D6-1ABEAA30300E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E042C9-1363-41D7-AAF4-2CB82A7EB7C6}"/>
 </file>